--- a/yolo/엘리베이터_객체인식_클래스_1차.xlsx
+++ b/yolo/엘리베이터_객체인식_클래스_1차.xlsx
@@ -13,7 +13,7 @@
     <sheet name="불합격 행 → 클래스" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'클래스'!$A$1:$K$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'클래스'!$A$1:$K$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -63,12 +63,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="007F7F7F"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="007F7F7F"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,13 +104,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -489,9 +489,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -527,9 +525,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -611,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -842,7 +838,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>주로프(매다는 장치)</t>
+          <t>주로프·현수벨트(매다는 장치)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -852,7 +848,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>주로프, 와이어로프, 현수로프, 매다는 장치, 스트랜드</t>
+          <t>주로프, 와이어로프, 현수로프, 매다는 장치, 스트랜드, 벨트, 플랫벨트, 현수 벨트</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -891,24 +887,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>로프 단말(소켓·클립)</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>기계실·구동부</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>소켓, 클립, 로프 단말, 끝부분의 고정</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>9.2 매다는 장치(현수), 보상수단 및 관련 보호수단 — 권상 도르래‧풀리 또는 드럼과 로프(…</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n">
         <v>5</v>
       </c>
@@ -925,7 +909,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1332,24 +1316,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>카·균형추 가이드슈(가이드롤러)</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>승강로</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>가이드 슈, 가이드슈, 가이드롤러, 가이드 롤러</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>13.3.1.2 일반사항 — 여러 개의 잭이 있는 경우, 잭은 압… / 11.2.1.2 일반사항 — 엘리베이터의 안전한 작동을 보장하기…</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n">
         <v>16</v>
       </c>
@@ -1366,7 +1338,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1430,24 +1402,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>로프·체인 이완감지 스위치</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>승강로</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>이완, 느슨, 슬랙</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>9.5.3 매다는 장치 사이의 하중 분산 — 매다는 장치가 비정상적으로 늘어난 경…</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n">
         <v>9</v>
       </c>
@@ -1464,7 +1424,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1724,24 +1684,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>행거·행거롤러</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>승강로(승강장문 뒤)</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>행거</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>7.3.2.2 출입문 안내수단 — 수평 개폐식 승강장문 및 카문은 상부… / 7.11.1 여러 문짝이 기계적으로 연결된 개폐식 승강장문 — 개폐식 승강장문이 기계적으로 직접 연…</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
       <c r="G23" s="3" t="n">
         <v>4</v>
       </c>
@@ -1758,7 +1706,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1773,24 +1721,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>도어 연동로프</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>승강로(승강장문 뒤)</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>연동로프, 연동 로프, 기계적으로 연결, 연동</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>7.11 여러 문짝이 기계적으로 연결된 개폐식 승강장문</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
       <c r="G24" s="3" t="n">
         <v>16</v>
       </c>
@@ -1807,7 +1743,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2018,24 +1954,12 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>도어머신(문 개폐장치)</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>카 상부·피트</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>도어머신, 개폐장치, 도어개폐장치</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>7.15.1 카문의 개방 — 엘리베이터가 어떤 이유로 인해 잠금해…</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
       <c r="G29" s="3" t="n">
         <v>5</v>
       </c>
@@ -2052,7 +1976,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2116,24 +2040,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>카문 닫힘 스위치(게이트 스위치)</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>카 상부·피트</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>카문의 닫힘, 카 문 닫힘, 카문 스위치, 게이트 스위치</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>7.13 카문의 닫힘을 입증하는 전기안전장치</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
       <c r="G31" s="3" t="n">
         <v>5</v>
       </c>
@@ -2150,7 +2062,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2263,24 +2175,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>문 가이드슈(도어슈)</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>승강장·카</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>가이드슈, 가이드 슈, 도어슈, 안내수단</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>7.3.2 출입문 안내수단</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
       <c r="G34" s="3" t="n">
         <v>19</v>
       </c>
@@ -2297,7 +2197,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2361,24 +2261,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>전망창(방범창)</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>승강장·카</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>전망창, 투명유리창, 방범창</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>7.7.2.2 &lt;&lt;카 있음&gt;&gt; 신호 표시 — 카문이 자동이 아니고 카가 승강장에서…</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n"/>
       <c r="G36" s="3" t="n">
         <v>4</v>
       </c>
@@ -2395,7 +2283,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2410,24 +2298,12 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>과부하감지장치(하중검출)</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>카</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>과부하</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>16.1.2 부하 제어</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
       <c r="G37" s="3" t="n">
         <v>9</v>
       </c>
@@ -2444,7 +2320,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2704,24 +2580,12 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>비상운전·작동시험 패널</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>승강장·건물(MRL)</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>작동시험, 비상운전 및 작동시험</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>6.6.6 비상운전 및 작동시험을 위한 장치</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="n">
         <v>23</v>
       </c>
@@ -2738,7 +2602,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2753,24 +2617,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>유리(문짝·카 벽·승강로 벽)</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>유리</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>6.1.8.3 벽, 바닥 및 천장의 강도 — 평면‧성형 유리판은 KS L 2004… / 7.5.3.4 기계적 강도 — 유리판이 있는 승강장문, 유리판이 있… / 8.3.2.3 카의 벽, 바닥 및 지붕 — 카 벽 전체 또는 일부에 사용되는 유…</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n"/>
       <c r="G44" s="3" t="n">
         <v>17</v>
       </c>
@@ -2787,7 +2639,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2892,24 +2744,12 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>현수 벨트(플랫벨트)</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>기계실·구동부</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>벨트, 플랫벨트</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>9.1 매다는 장치(현수)</t>
-        </is>
-      </c>
+          <t>(통합 → 3 주로프 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n"/>
       <c r="G47" s="3" t="n">
         <v>20</v>
       </c>
@@ -2922,7 +2762,7 @@
       <c r="J47" s="3" t="inlineStr"/>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3113,24 +2953,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>안내·경고 표지</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>기계실·구동부</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>표지, 경고, 안내문, 주의사항</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>6.4 표시 / 6.6.2 안내표지 및 설명서</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n"/>
       <c r="G52" s="3" t="n">
         <v>16</v>
       </c>
@@ -3143,7 +2971,7 @@
       <c r="J52" s="3" t="inlineStr"/>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3203,24 +3031,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>레일 브라켓</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>승강로</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>브라켓, 브래킷, 지지대</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>Ⅵ.2 주행안내 레일의 지지대</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
       <c r="G54" s="3" t="n">
         <v>24</v>
       </c>
@@ -3233,7 +3049,7 @@
       <c r="J54" s="3" t="inlineStr"/>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3293,24 +3109,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>착상장치(차폐판·착상센서)</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>승강로</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>차폐판, 착상, 재-착상, 자석</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>16.1.1 정상운전 제어</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
       <c r="G56" s="3" t="n">
         <v>13</v>
       </c>
@@ -3323,7 +3127,7 @@
       <c r="J56" s="3" t="inlineStr"/>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3338,37 +3142,25 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>이동케이블</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>승강로</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>이동케이블, 이동 케이블</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>14.6.5 이동케이블</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr"/>
       <c r="G57" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="3" t="inlineStr"/>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3473,24 +3265,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>비상구출문(카 지붕)</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>카 상부·피트</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>비상구출문, 비상구출구, 구출구</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>8.6 비상구출문</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
       <c r="G60" s="3" t="n">
         <v>16</v>
       </c>
@@ -3503,7 +3283,7 @@
       <c r="J60" s="3" t="inlineStr"/>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3608,24 +3388,12 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>집수정(피트 배수)</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>카 상부·피트</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>집수정, 배수</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>6.1.9.3 벽, 바닥 및 천장의 재질 — 피트는 주행안내 레일 고정 장치, 완…</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n"/>
+      <c r="E63" s="3" t="n"/>
+      <c r="F63" s="3" t="n"/>
       <c r="G63" s="3" t="n">
         <v>3</v>
       </c>
@@ -3638,7 +3406,7 @@
       <c r="J63" s="3" t="inlineStr"/>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3923,24 +3691,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>정격하중·정원 표시</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>카</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>정원, 정격하중</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>8.2.3 정원</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n"/>
       <c r="G70" s="3" t="n">
         <v>60</v>
       </c>
@@ -3953,7 +3709,7 @@
       <c r="J70" s="3" t="inlineStr"/>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4148,24 +3904,12 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>환기설비(환풍기·환기구)</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>환기, 환풍기</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>6.1.3 승강로, 기계실ㆍ기계류 공간 및 풀리실의 환기 / 8.9 환기</t>
-        </is>
-      </c>
+          <t>(삭제 — 번호만 유지, 라벨 달지 말 것)</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n"/>
       <c r="G75" s="3" t="n">
         <v>15</v>
       </c>
@@ -4178,7 +3922,7 @@
       <c r="J75" s="3" t="inlineStr"/>
       <c r="K75" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4227,8 +3971,98 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>tension_weight</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>과속조절기 로프 인장추(인장 풀리)</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>카 상부·피트</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>인장추, 인장 풀리, 인장풀리, 인장 도르래</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>10.2.2.1.3 과속조절기 로프</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr"/>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>toe_board</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>카 지붕 발보호판</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>카 상부·피트</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>발보호판, 발 보호판, 토보드</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>8.7.2 카 지붕 — 카 지붕에는 다음과 같은 보호수단이…</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr"/>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K76"/>
+  <autoFilter ref="A1:K78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4255,52 +4089,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>클래스 키(영문)</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>한글 이름</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>위치</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>별칭·현장용어(라벨러 참고)</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>근거 조항(별표22, 연혁집 현행)</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>조문 언급 수</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>표준화 언급 수</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>불합격 행 수</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>관련 불합격 항목(지침 별표2)</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
@@ -4740,27 +4574,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>조항</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>검사대상</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>불합격 내용</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>클래스</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>탐지 대상 아님 이유</t>
         </is>
@@ -4790,24 +4624,24 @@
       <c r="E2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>6.1.9.3</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>피트 구획/누수</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>· 피트 구획 안됨
 · 피트 침수(발목이상 잠김)로 피트 검사 불가</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr"/>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>장소 상태(구획·침수) — 물건 아님</t>
         </is>
@@ -4837,92 +4671,92 @@
       <c r="E4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>6.5.1.3</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>승강로내 돌출물</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>· 승강로 내 돌출물이 카의 안전운행에 지장을 줌</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>장소 상태</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>6.5.1.5</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>승강로 누수</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>· 천정 및 승강로 누수로 인한 카 상부 물 고임 또는 물 낙하</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>장소 상태(누수)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>6.5.2.1</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>승강로 구획</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>· 승강로 구획 안됨</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>장소 상태(구획)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>6.5.2.3</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>반밀폐식 승강로</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>· 승강로 벽 미설치</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>벽 유무 — 장소 상태</t>
         </is>
@@ -4952,46 +4786,46 @@
       <c r="E9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>6.6.4.3.1</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>카내부 또는 카 지붕의 작업구역</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>· 기계적인 장치 미설치 및 전기안전장치 미작동</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>기계적 장치 외형이 제조사마다 다름 — 사진 모은 뒤 결정</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>6.6.4.4.1</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>피트 내부의 작업구역</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>· 기계적인 장치 미설치 및 전기안전장치 미작동</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>위와 같음</t>
         </is>
@@ -5069,23 +4903,23 @@
       <c r="E14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>7.1.1</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>2개 이상의 카 출입구</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>· 2개 이상의 양방향 출입구가 동시에 열림</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>동작 판정</t>
         </is>
@@ -5456,24 +5290,24 @@
       <c r="E30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>7.10.1</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>잠금/닫힘 정상 시퀀스의 구성</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>· 승강장문 도어단락 감지장치 미작동
 (기능 상실)</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr"/>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>제어 기능(도어단락 감지)</t>
         </is>
@@ -5527,69 +5361,69 @@
       <c r="E33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>8.3.1</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>카의 밀폐식 구획</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>· 카(벽/지붕/바닥 등) 구획 안됨</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr"/>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr"/>
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>카 구획 상태</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>8.3.2</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>카의 조립체</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>· 카 상부 또는 카 바닥 붕괴 있음</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr"/>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr"/>
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>붕괴 상태</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>8.3.2.1</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>카 바닥의 기울기</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>· 추락방지안전장치 작동 시 카 바닥 기울기 초과</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr"/>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>측정 판정</t>
         </is>
@@ -5906,24 +5740,24 @@
       <c r="E49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>10.2.2.3</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>시험 후 안전 안전로프/관련 부품 상태</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>· 정상작동 후 심각한 손상 있음
 · 추락방지안전장치 작동 전 안전로프 슬립 발생</t>
         </is>
       </c>
-      <c r="D50" s="8" t="inlineStr"/>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr"/>
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>안전로프(유압 간접식) — 사례 드묾, 필요시 추가</t>
         </is>
@@ -5953,23 +5787,23 @@
       <c r="E51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>10.4.1</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>유량제한기</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>· 유량제한기 미작동(추락방지안전장치 미설치 시)</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr"/>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr"/>
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>밸브 블록 내부 — 겉모습은 파워유니트</t>
         </is>
@@ -6046,46 +5880,46 @@
       <c r="E55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>10.7.1</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>개문출발 방지장치</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>· 개문출발방지장치 미작동(기능 상실)</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr"/>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr"/>
+      <c r="E56" s="6" t="inlineStr">
         <is>
           <t>전용 외형 없음(브레이크·제어 기능)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>10.7.5</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>개문출발 방지장치 정지거리</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>· 개문출발방지장치 정지거리 초과</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr"/>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr"/>
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>측정 판정</t>
         </is>
@@ -6355,24 +6189,24 @@
       <c r="E68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>13.3.5.2.2</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>체크밸브 작동</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>· 체크밸브 미작동
 (전원 차단 시 제 위치 유지 안됨)</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr"/>
-      <c r="E69" s="8" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr"/>
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>밸브 블록 내부</t>
         </is>
@@ -6402,92 +6236,92 @@
       <c r="E70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>13.3.10.2</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>전동기 공회전 방지장치</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>· 공회전방지장치 미작동</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr"/>
-      <c r="E71" s="8" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr"/>
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>제어 기능</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>14.1.3.1</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>전기설비의 절연저항</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>· 각 회로 절연저항 측정값 기준 미만</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr"/>
-      <c r="E72" s="8" t="inlineStr">
+      <c r="D72" s="6" t="inlineStr"/>
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>측정 판정(계측기)</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>15.2.1.1 · 15.2.4</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>전기안전장치</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>· 제어회로의 이상으로 인한 오동작 발생
 · 안전과 관련회로를 인위적으로 단락시킨 경우
 · 전기안전장치 작동 시 구동기 정지 안됨</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr"/>
-      <c r="E73" s="8" t="inlineStr"/>
+      <c r="D73" s="6" t="inlineStr"/>
+      <c r="E73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>16.1.1.4</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>카의 정상 착상/ 재-착상 정확도</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>· 승강장 호출 시 카가 정상적으로 도착하지 않음
 (±60mm 초과 착상오차 발생 시)
 · 카가 호출 층에 도착하지 않음</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr"/>
-      <c r="E74" s="8" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr"/>
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>동작·측정 판정</t>
         </is>
@@ -6564,23 +6398,23 @@
       <c r="E77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>16.1.10</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>전기적 크리핑방지 시스템</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>· 전기적 크리핑방지 시스템 미작동</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr"/>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="D78" s="6" t="inlineStr"/>
+      <c r="E78" s="6" t="inlineStr">
         <is>
           <t>제어 기능</t>
         </is>
